--- a/franchises.xlsx
+++ b/franchises.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/pythonProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCAB2D1-B1BB-1643-AAA9-7AAB243CAA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB6C1A4-CC96-6446-9598-441ABE2A025F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17400" xr2:uid="{560E9FB9-65B9-9A4C-9447-806357BA28D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -522,12 +522,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -539,7 +547,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -547,12 +555,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -888,585 +935,585 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC382C8-FAC7-9345-92A5-4AC6D3C427D2}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.5" customWidth="1"/>
-    <col min="2" max="2" width="37.1640625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
-    <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" customWidth="1"/>
-    <col min="8" max="8" width="57.6640625" customWidth="1"/>
-    <col min="9" max="9" width="49.1640625" customWidth="1"/>
-    <col min="10" max="10" width="38.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
-    <col min="12" max="12" width="45.5" customWidth="1"/>
-    <col min="13" max="13" width="31.1640625" customWidth="1"/>
+    <col min="1" max="1" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="44.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="19" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="20" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    <row r="21" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="22" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="24" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="25" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="26" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="27" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="29" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="32" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="34" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
     </row>

--- a/franchises.xlsx
+++ b/franchises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB6C1A4-CC96-6446-9598-441ABE2A025F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135DB746-AF23-F548-82F0-B12B9BDCD8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17400" xr2:uid="{560E9FB9-65B9-9A4C-9447-806357BA28D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="165">
   <si>
     <t>MCU</t>
   </si>
@@ -516,6 +516,21 @@
   </si>
   <si>
     <t>Aquaman</t>
+  </si>
+  <si>
+    <t>Elio</t>
+  </si>
+  <si>
+    <t>Captain America: Brave New World</t>
+  </si>
+  <si>
+    <t>Thunderbolts*</t>
+  </si>
+  <si>
+    <t>The Fantastic Four: First Steps</t>
+  </si>
+  <si>
+    <t>Jurassic World Rebirth</t>
   </si>
 </sst>
 </file>
@@ -587,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -600,6 +615,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC382C8-FAC7-9345-92A5-4AC6D3C427D2}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.1640625" bestFit="1" customWidth="1"/>
@@ -1240,6 +1256,9 @@
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="C8" s="6" t="s">
+        <v>164</v>
+      </c>
       <c r="D8" s="3" t="s">
         <v>58</v>
       </c>
@@ -1491,6 +1510,9 @@
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="D30" s="3" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
@@ -1515,6 +1537,21 @@
     <row r="35" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/franchises.xlsx
+++ b/franchises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135DB746-AF23-F548-82F0-B12B9BDCD8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2938D4-11B6-744E-9DF1-563BEC500947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17400" xr2:uid="{560E9FB9-65B9-9A4C-9447-806357BA28D7}"/>
   </bookViews>
@@ -562,7 +562,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -598,6 +598,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -615,7 +628,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,10 +1085,10 @@
       <c r="G3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="6" t="s">
         <v>128</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -1113,10 +1126,10 @@
       <c r="G4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="6" t="s">
         <v>129</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -1154,10 +1167,10 @@
       <c r="G5" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="6" t="s">
         <v>130</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -1195,10 +1208,10 @@
       <c r="G6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="6" t="s">
         <v>131</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -1236,10 +1249,10 @@
       <c r="G7" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="6" t="s">
         <v>132</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -1256,7 +1269,7 @@
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>164</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -1271,7 +1284,7 @@
       <c r="H8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1540,17 +1553,17 @@
       </c>
     </row>
     <row r="36" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="3" t="s">
         <v>163</v>
       </c>
     </row>
